--- a/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
+++ b/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cieredu-my.sharepoint.com/personal/sylu90_cier_edu_tw/Documents/桌面/每月PMI &amp; NMI/2026年1月PMI&amp;NMI/4.1 PMI/【1月】PMI (季調後) 相關檔案 20260126修正版/英文版/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cieredu-my.sharepoint.com/personal/sylu90_cier_edu_tw/Documents/桌面/每月PMI &amp; NMI/2026年2月PMI&amp;NMI/4.1 PMI/【季調後】PMI整包編制_20260304/英文版/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{C8F0B239-31EA-4772-B165-90B417EDD71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA40E88B-C2D4-47B9-9740-8D35B1A4C8F5}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="8_{C8F0B239-31EA-4772-B165-90B417EDD71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2C3356F-1B04-4218-8500-2BD4D6C399AD}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,13 +22,13 @@
     <sheet name="Electrical &amp; Machinery" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$166</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$166</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -378,6 +378,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -387,31 +399,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -430,6 +430,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -722,7 +726,7 @@
   <sheetPr codeName="工作表1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -730,92 +734,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="32" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -8965,6 +8969,56 @@
       </c>
       <c r="P166" s="7">
         <v>66</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="21">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="17">
+        <v>58.5</v>
+      </c>
+      <c r="C167" s="17">
+        <v>63.7</v>
+      </c>
+      <c r="D167" s="17">
+        <v>59.8</v>
+      </c>
+      <c r="E167" s="17">
+        <v>52.8</v>
+      </c>
+      <c r="F167" s="17">
+        <v>59.5</v>
+      </c>
+      <c r="G167" s="17">
+        <v>56.7</v>
+      </c>
+      <c r="H167" s="17">
+        <v>47.7</v>
+      </c>
+      <c r="I167" s="17">
+        <v>76.2</v>
+      </c>
+      <c r="J167" s="17">
+        <v>55</v>
+      </c>
+      <c r="K167" s="17">
+        <v>52.6</v>
+      </c>
+      <c r="L167" s="17">
+        <v>51.7</v>
+      </c>
+      <c r="M167" s="17">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="N167" s="7">
+        <v>43</v>
+      </c>
+      <c r="O167" s="7">
+        <v>35</v>
+      </c>
+      <c r="P167" s="7">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -8999,7 +9053,7 @@
   <sheetPr codeName="工作表2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="13" width="12.125" customWidth="1"/>
@@ -9007,90 +9061,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -17242,12 +17296,58 @@
         <v>77</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="21">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="C167" s="11">
+        <v>43.2</v>
+      </c>
+      <c r="D167" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="E167" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="F167" s="11">
+        <v>53.4</v>
+      </c>
+      <c r="G167" s="11">
+        <v>54.5</v>
+      </c>
+      <c r="H167" s="11">
+        <v>45.5</v>
+      </c>
+      <c r="I167" s="11">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="J167" s="11">
+        <v>44.3</v>
+      </c>
+      <c r="K167" s="11">
+        <v>42</v>
+      </c>
+      <c r="L167" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="M167" s="11">
+        <v>59.1</v>
+      </c>
+      <c r="N167" s="15">
+        <v>35</v>
+      </c>
+      <c r="O167" s="15">
+        <v>31</v>
+      </c>
+      <c r="P167" s="15">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -17261,6 +17361,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -17273,7 +17377,7 @@
   <sheetPr codeName="工作表3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -17290,90 +17394,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -25525,12 +25629,58 @@
         <v>70</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="21">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="17">
+        <v>55.1</v>
+      </c>
+      <c r="C167" s="17">
+        <v>56.8</v>
+      </c>
+      <c r="D167" s="17">
+        <v>46.8</v>
+      </c>
+      <c r="E167" s="17">
+        <v>51.8</v>
+      </c>
+      <c r="F167" s="17">
+        <v>62.2</v>
+      </c>
+      <c r="G167" s="17">
+        <v>58.1</v>
+      </c>
+      <c r="H167" s="17">
+        <v>47.7</v>
+      </c>
+      <c r="I167" s="17">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="J167" s="17">
+        <v>59.9</v>
+      </c>
+      <c r="K167" s="17">
+        <v>56.3</v>
+      </c>
+      <c r="L167" s="17">
+        <v>54.5</v>
+      </c>
+      <c r="M167" s="17">
+        <v>66.7</v>
+      </c>
+      <c r="N167" s="7">
+        <v>50</v>
+      </c>
+      <c r="O167" s="7">
+        <v>36</v>
+      </c>
+      <c r="P167" s="7">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -25544,6 +25694,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -25556,7 +25710,7 @@
   <sheetPr codeName="工作表4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -25573,90 +25727,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -33808,12 +33962,58 @@
         <v>53</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="21">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="C167" s="11">
+        <v>45.8</v>
+      </c>
+      <c r="D167" s="11">
+        <v>37.5</v>
+      </c>
+      <c r="E167" s="11">
+        <v>45.8</v>
+      </c>
+      <c r="F167" s="11">
+        <v>56.3</v>
+      </c>
+      <c r="G167" s="11">
+        <v>52.1</v>
+      </c>
+      <c r="H167" s="11">
+        <v>52.1</v>
+      </c>
+      <c r="I167" s="11">
+        <v>66.7</v>
+      </c>
+      <c r="J167" s="11">
+        <v>45.8</v>
+      </c>
+      <c r="K167" s="11">
+        <v>52.1</v>
+      </c>
+      <c r="L167" s="11">
+        <v>47.9</v>
+      </c>
+      <c r="M167" s="11">
+        <v>60.4</v>
+      </c>
+      <c r="N167" s="15">
+        <v>49</v>
+      </c>
+      <c r="O167" s="15">
+        <v>31</v>
+      </c>
+      <c r="P167" s="15">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -33827,6 +34027,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -33839,7 +34043,7 @@
   <sheetPr codeName="工作表5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -33856,90 +34060,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -42091,12 +42295,58 @@
         <v>58</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="11">
+        <v>45.2</v>
+      </c>
+      <c r="C167" s="11">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="D167" s="11">
+        <v>29.3</v>
+      </c>
+      <c r="E167" s="11">
+        <v>46.7</v>
+      </c>
+      <c r="F167" s="11">
+        <v>53.3</v>
+      </c>
+      <c r="G167" s="11">
+        <v>56.5</v>
+      </c>
+      <c r="H167" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="I167" s="11">
+        <v>72.8</v>
+      </c>
+      <c r="J167" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="K167" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="L167" s="11">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="M167" s="11">
+        <v>59.8</v>
+      </c>
+      <c r="N167" s="15">
+        <v>45</v>
+      </c>
+      <c r="O167" s="15">
+        <v>44</v>
+      </c>
+      <c r="P167" s="15">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -42110,6 +42360,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -42122,7 +42376,7 @@
   <sheetPr codeName="工作表6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -42139,90 +42393,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -50374,12 +50628,58 @@
         <v>76</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="C167" s="11">
+        <v>47.4</v>
+      </c>
+      <c r="D167" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="E167" s="11">
+        <v>44.7</v>
+      </c>
+      <c r="F167" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="G167" s="11">
+        <v>50</v>
+      </c>
+      <c r="H167" s="11">
+        <v>42.1</v>
+      </c>
+      <c r="I167" s="11">
+        <v>65.8</v>
+      </c>
+      <c r="J167" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="K167" s="11">
+        <v>50</v>
+      </c>
+      <c r="L167" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="M167" s="11">
+        <v>44.7</v>
+      </c>
+      <c r="N167" s="15">
+        <v>24</v>
+      </c>
+      <c r="O167" s="15">
+        <v>24</v>
+      </c>
+      <c r="P167" s="15">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -50393,6 +50693,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -50405,7 +50709,7 @@
   <sheetPr codeName="工作表7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -50421,90 +50725,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="23"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="27"/>
+      <c r="B1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="L2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="28" t="s">
+      <c r="O2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="25"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -58656,12 +58960,58 @@
         <v>54</v>
       </c>
     </row>
+    <row r="167" spans="1:16" ht="18" customHeight="1">
+      <c r="A167" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B167" s="16">
+        <v>48.6</v>
+      </c>
+      <c r="C167" s="16">
+        <v>45.3</v>
+      </c>
+      <c r="D167" s="16">
+        <v>41.9</v>
+      </c>
+      <c r="E167" s="16">
+        <v>50</v>
+      </c>
+      <c r="F167" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G167" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="H167" s="16">
+        <v>46.5</v>
+      </c>
+      <c r="I167" s="16">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="J167" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="K167" s="16">
+        <v>47.7</v>
+      </c>
+      <c r="L167" s="16">
+        <v>50</v>
+      </c>
+      <c r="M167" s="16">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="N167" s="18">
+        <v>38</v>
+      </c>
+      <c r="O167" s="18">
+        <v>34</v>
+      </c>
+      <c r="P167" s="18">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -58675,6 +59025,10 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
+++ b/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cieredu-my.sharepoint.com/personal/sylu90_cier_edu_tw/Documents/桌面/每月PMI &amp; NMI/2026年2月PMI&amp;NMI/4.1 PMI/【季調後】PMI整包編制_20260304/英文版/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sprice\Desktop\徐晨堯\每月PMI&amp;NMI\3月PMI&amp;NMI\編制\PMI\0325_PMI季調後\【未季調】2026 03 PMI 整包編制檔案\英文版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="8_{C8F0B239-31EA-4772-B165-90B417EDD71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2C3356F-1B04-4218-8500-2BD4D6C399AD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BD8C80-3B00-4844-BB29-0F3895F0A34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,13 +22,13 @@
     <sheet name="Electrical &amp; Machinery" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$168</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -379,16 +379,25 @@
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -399,19 +408,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -430,10 +430,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,7 +722,7 @@
   <sheetPr codeName="工作表1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -734,92 +730,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="33" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="30" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -9021,8 +9017,63 @@
         <v>65</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="21">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="17">
+        <v>55.4</v>
+      </c>
+      <c r="C168" s="17">
+        <v>52.1</v>
+      </c>
+      <c r="D168" s="17">
+        <v>48.3</v>
+      </c>
+      <c r="E168" s="17">
+        <v>51.1</v>
+      </c>
+      <c r="F168" s="17">
+        <v>66.3</v>
+      </c>
+      <c r="G168" s="17">
+        <v>59.4</v>
+      </c>
+      <c r="H168" s="17">
+        <v>47.8</v>
+      </c>
+      <c r="I168" s="17">
+        <v>86</v>
+      </c>
+      <c r="J168" s="17">
+        <v>61.4</v>
+      </c>
+      <c r="K168" s="17">
+        <v>64.2</v>
+      </c>
+      <c r="L168" s="17">
+        <v>62.7</v>
+      </c>
+      <c r="M168" s="17">
+        <v>61</v>
+      </c>
+      <c r="N168" s="7">
+        <v>45</v>
+      </c>
+      <c r="O168" s="7">
+        <v>35</v>
+      </c>
+      <c r="P168" s="7">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:P1"/>
@@ -9036,11 +9087,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9053,7 +9099,7 @@
   <sheetPr codeName="工作表2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="2" max="13" width="12.125" customWidth="1"/>
@@ -9061,90 +9107,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -17346,8 +17392,59 @@
         <v>64</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="21">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="11">
+        <v>52.9</v>
+      </c>
+      <c r="C168" s="11">
+        <v>53.6</v>
+      </c>
+      <c r="D168" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="E168" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="F168" s="11">
+        <v>64.3</v>
+      </c>
+      <c r="G168" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="H168" s="11">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="I168" s="11">
+        <v>85.7</v>
+      </c>
+      <c r="J168" s="11">
+        <v>53.6</v>
+      </c>
+      <c r="K168" s="11">
+        <v>56</v>
+      </c>
+      <c r="L168" s="11">
+        <v>63.1</v>
+      </c>
+      <c r="M168" s="11">
+        <v>44</v>
+      </c>
+      <c r="N168" s="15">
+        <v>37</v>
+      </c>
+      <c r="O168" s="15">
+        <v>30</v>
+      </c>
+      <c r="P168" s="15">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -17364,7 +17461,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -17377,7 +17473,7 @@
   <sheetPr codeName="工作表3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -17394,90 +17490,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -25679,8 +25775,59 @@
         <v>71</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="21">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="17">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="C168" s="17">
+        <v>71.8</v>
+      </c>
+      <c r="D168" s="17">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="E168" s="17">
+        <v>51.9</v>
+      </c>
+      <c r="F168" s="17">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="G168" s="17">
+        <v>62</v>
+      </c>
+      <c r="H168" s="17">
+        <v>48.1</v>
+      </c>
+      <c r="I168" s="17">
+        <v>86.6</v>
+      </c>
+      <c r="J168" s="17">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="K168" s="17">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="L168" s="17">
+        <v>66.2</v>
+      </c>
+      <c r="M168" s="17">
+        <v>64.8</v>
+      </c>
+      <c r="N168" s="7">
+        <v>52</v>
+      </c>
+      <c r="O168" s="7">
+        <v>35</v>
+      </c>
+      <c r="P168" s="7">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -25697,7 +25844,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -25710,7 +25856,7 @@
   <sheetPr codeName="工作表4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -25727,90 +25873,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -34012,8 +34158,59 @@
         <v>53</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="21">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="11">
+        <v>60</v>
+      </c>
+      <c r="C168" s="11">
+        <v>62.5</v>
+      </c>
+      <c r="D168" s="11">
+        <v>60.4</v>
+      </c>
+      <c r="E168" s="11">
+        <v>58.3</v>
+      </c>
+      <c r="F168" s="11">
+        <v>60.4</v>
+      </c>
+      <c r="G168" s="11">
+        <v>58.3</v>
+      </c>
+      <c r="H168" s="11">
+        <v>56.3</v>
+      </c>
+      <c r="I168" s="11">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="J168" s="11">
+        <v>52.1</v>
+      </c>
+      <c r="K168" s="11">
+        <v>56.3</v>
+      </c>
+      <c r="L168" s="11">
+        <v>62.5</v>
+      </c>
+      <c r="M168" s="11">
+        <v>50</v>
+      </c>
+      <c r="N168" s="15">
+        <v>49</v>
+      </c>
+      <c r="O168" s="15">
+        <v>46</v>
+      </c>
+      <c r="P168" s="15">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -34030,7 +34227,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -34043,7 +34239,7 @@
   <sheetPr codeName="工作表5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -34060,90 +34256,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -42345,8 +42541,59 @@
         <v>70</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="8">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="C168" s="11">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="D168" s="11">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="E168" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F168" s="11">
+        <v>58.1</v>
+      </c>
+      <c r="G168" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="H168" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="I168" s="11">
+        <v>91.9</v>
+      </c>
+      <c r="J168" s="11">
+        <v>59.3</v>
+      </c>
+      <c r="K168" s="11">
+        <v>54.7</v>
+      </c>
+      <c r="L168" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="M168" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="N168" s="15">
+        <v>49</v>
+      </c>
+      <c r="O168" s="15">
+        <v>39</v>
+      </c>
+      <c r="P168" s="15">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -42363,7 +42610,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -42376,7 +42622,7 @@
   <sheetPr codeName="工作表6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -42393,90 +42639,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -50678,8 +50924,59 @@
         <v>87</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="8">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="C168" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="D168" s="11">
+        <v>63.2</v>
+      </c>
+      <c r="E168" s="11">
+        <v>50</v>
+      </c>
+      <c r="F168" s="11">
+        <v>63.2</v>
+      </c>
+      <c r="G168" s="11">
+        <v>65.8</v>
+      </c>
+      <c r="H168" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="I168" s="11">
+        <v>73.7</v>
+      </c>
+      <c r="J168" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="K168" s="11">
+        <v>44.7</v>
+      </c>
+      <c r="L168" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="M168" s="11">
+        <v>44.7</v>
+      </c>
+      <c r="N168" s="15">
+        <v>32</v>
+      </c>
+      <c r="O168" s="15">
+        <v>33</v>
+      </c>
+      <c r="P168" s="15">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -50696,7 +50993,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -50709,7 +51005,7 @@
   <sheetPr codeName="工作表7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -50725,90 +51021,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="27"/>
-      <c r="B1" s="30" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="L2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
       <c r="A4" s="2">
@@ -59010,8 +59306,59 @@
         <v>42</v>
       </c>
     </row>
+    <row r="168" spans="1:16" ht="18" customHeight="1">
+      <c r="A168" s="8">
+        <v>46082</v>
+      </c>
+      <c r="B168" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="C168" s="16">
+        <v>61.6</v>
+      </c>
+      <c r="D168" s="16">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="E168" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="F168" s="16">
+        <v>60.5</v>
+      </c>
+      <c r="G168" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="H168" s="16">
+        <v>41.9</v>
+      </c>
+      <c r="I168" s="16">
+        <v>82.6</v>
+      </c>
+      <c r="J168" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="K168" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="L168" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="M168" s="16">
+        <v>57</v>
+      </c>
+      <c r="N168" s="18">
+        <v>33</v>
+      </c>
+      <c r="O168" s="18">
+        <v>32</v>
+      </c>
+      <c r="P168" s="18">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="P2:P3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:P1"/>
     <mergeCell ref="B2:B3"/>
@@ -59028,7 +59375,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
+++ b/backend/data/excel/PMI_Historical_Data_Seasonally_Adjusted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seanchang0103\Desktop\張恒碩\每月PMI&amp;NMI\5月PMI&amp;NMI\【5月】PMI(季調後)\英文版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seanchang0103\Desktop\張恒碩\每月PMI&amp;NMI\6月PMI&amp;NMI\【6月】PMI(季調後)\英文版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5073BEAB-ED46-4DDB-8935-2B6F1506D2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E4F72B-C673-461C-BFFE-603EAEA6124A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="947" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="947" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taiwan Manufacturing PMI" sheetId="1" r:id="rId1"/>
@@ -22,13 +22,13 @@
     <sheet name="Electrical &amp; Machinery" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$170</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$170</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Basic Materials industry'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Chemical, Biological &amp; Medical'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Electrical &amp; Machinery'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Electronic &amp; Optical industry'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Foods &amp; Textiles industry '!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Taiwan Manufacturing PMI'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Transportation Equipment'!$A$1:$P$171</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -378,27 +378,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -412,6 +391,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -722,7 +722,7 @@
   <sheetPr codeName="工作表1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -730,92 +730,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -9167,13 +9167,58 @@
         <v>71</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="17">
+        <v>60.7</v>
+      </c>
+      <c r="C171" s="17">
+        <v>60.4</v>
+      </c>
+      <c r="D171" s="17">
+        <v>58.7</v>
+      </c>
+      <c r="E171" s="17">
+        <v>55.4</v>
+      </c>
+      <c r="F171" s="17">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="G171" s="17">
+        <v>61.9</v>
+      </c>
+      <c r="H171" s="17">
+        <v>49.4</v>
+      </c>
+      <c r="I171" s="17">
+        <v>76.3</v>
+      </c>
+      <c r="J171" s="17">
+        <v>60.9</v>
+      </c>
+      <c r="K171" s="17">
+        <v>63.1</v>
+      </c>
+      <c r="L171" s="17">
+        <v>65</v>
+      </c>
+      <c r="M171" s="17">
+        <v>64.2</v>
+      </c>
+      <c r="N171" s="7">
+        <v>46</v>
+      </c>
+      <c r="O171" s="7">
+        <v>38</v>
+      </c>
+      <c r="P171" s="7">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:P1"/>
@@ -9187,6 +9232,11 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -9199,7 +9249,7 @@
   <sheetPr codeName="工作表2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="13" width="12.125" customWidth="1"/>
@@ -9207,90 +9257,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -17642,8 +17692,59 @@
         <v>57</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="11">
+        <v>50.9</v>
+      </c>
+      <c r="C171" s="11">
+        <v>47.7</v>
+      </c>
+      <c r="D171" s="11">
+        <v>47.7</v>
+      </c>
+      <c r="E171" s="11">
+        <v>50</v>
+      </c>
+      <c r="F171" s="11">
+        <v>55.7</v>
+      </c>
+      <c r="G171" s="11">
+        <v>53.4</v>
+      </c>
+      <c r="H171" s="11">
+        <v>50</v>
+      </c>
+      <c r="I171" s="11">
+        <v>51.1</v>
+      </c>
+      <c r="J171" s="11">
+        <v>50</v>
+      </c>
+      <c r="K171" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="L171" s="11">
+        <v>51.1</v>
+      </c>
+      <c r="M171" s="11">
+        <v>51.1</v>
+      </c>
+      <c r="N171" s="15">
+        <v>35</v>
+      </c>
+      <c r="O171" s="15">
+        <v>30</v>
+      </c>
+      <c r="P171" s="15">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -17660,7 +17761,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -17673,7 +17773,7 @@
   <sheetPr codeName="工作表3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -17690,90 +17790,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -26125,8 +26225,59 @@
         <v>82</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="17">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C171" s="17">
+        <v>66.7</v>
+      </c>
+      <c r="D171" s="17">
+        <v>66.7</v>
+      </c>
+      <c r="E171" s="17">
+        <v>59.3</v>
+      </c>
+      <c r="F171" s="17">
+        <v>72.2</v>
+      </c>
+      <c r="G171" s="17">
+        <v>65.7</v>
+      </c>
+      <c r="H171" s="17">
+        <v>49.5</v>
+      </c>
+      <c r="I171" s="17">
+        <v>81</v>
+      </c>
+      <c r="J171" s="17">
+        <v>66.7</v>
+      </c>
+      <c r="K171" s="17">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="L171" s="17">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="M171" s="17">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="N171" s="7">
+        <v>54</v>
+      </c>
+      <c r="O171" s="7">
+        <v>39</v>
+      </c>
+      <c r="P171" s="7">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -26143,7 +26294,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -26156,7 +26306,7 @@
   <sheetPr codeName="工作表4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -26173,90 +26323,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -34608,8 +34758,59 @@
         <v>59</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="11">
+        <v>57</v>
+      </c>
+      <c r="C171" s="11">
+        <v>56.5</v>
+      </c>
+      <c r="D171" s="11">
+        <v>54.3</v>
+      </c>
+      <c r="E171" s="11">
+        <v>58.7</v>
+      </c>
+      <c r="F171" s="11">
+        <v>65.2</v>
+      </c>
+      <c r="G171" s="11">
+        <v>50</v>
+      </c>
+      <c r="H171" s="11">
+        <v>45.7</v>
+      </c>
+      <c r="I171" s="11">
+        <v>65.2</v>
+      </c>
+      <c r="J171" s="11">
+        <v>47.8</v>
+      </c>
+      <c r="K171" s="11">
+        <v>47.8</v>
+      </c>
+      <c r="L171" s="11">
+        <v>45.7</v>
+      </c>
+      <c r="M171" s="11">
+        <v>43.5</v>
+      </c>
+      <c r="N171" s="15">
+        <v>45</v>
+      </c>
+      <c r="O171" s="15">
+        <v>38</v>
+      </c>
+      <c r="P171" s="15">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -34626,7 +34827,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -34639,7 +34839,7 @@
   <sheetPr codeName="工作表5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -34656,90 +34856,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -43091,8 +43291,77 @@
         <v>63</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="11">
+        <v>52.7</v>
+      </c>
+      <c r="C171" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="D171" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="E171" s="11">
+        <v>47.7</v>
+      </c>
+      <c r="F171" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="G171" s="11">
+        <v>54.5</v>
+      </c>
+      <c r="H171" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="I171" s="11">
+        <v>61.4</v>
+      </c>
+      <c r="J171" s="11">
+        <v>46.6</v>
+      </c>
+      <c r="K171" s="11">
+        <v>55.7</v>
+      </c>
+      <c r="L171" s="11">
+        <v>55.7</v>
+      </c>
+      <c r="M171" s="11">
+        <v>55.7</v>
+      </c>
+      <c r="N171" s="15">
+        <v>57</v>
+      </c>
+      <c r="O171" s="15">
+        <v>47</v>
+      </c>
+      <c r="P171" s="15">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="8"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11"/>
+      <c r="G172" s="11"/>
+      <c r="H172" s="11"/>
+      <c r="I172" s="11"/>
+      <c r="J172" s="11"/>
+      <c r="K172" s="11"/>
+      <c r="L172" s="11"/>
+      <c r="M172" s="11"/>
+      <c r="N172" s="15"/>
+      <c r="O172" s="15"/>
+      <c r="P172" s="15"/>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -43109,7 +43378,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -43122,7 +43390,7 @@
   <sheetPr codeName="工作表6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -43139,90 +43407,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -51574,8 +51842,59 @@
         <v>107</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="11">
+        <v>57.6</v>
+      </c>
+      <c r="C171" s="11">
+        <v>52.4</v>
+      </c>
+      <c r="D171" s="11">
+        <v>69</v>
+      </c>
+      <c r="E171" s="11">
+        <v>50</v>
+      </c>
+      <c r="F171" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="G171" s="11">
+        <v>57.1</v>
+      </c>
+      <c r="H171" s="11">
+        <v>47.6</v>
+      </c>
+      <c r="I171" s="11">
+        <v>85.7</v>
+      </c>
+      <c r="J171" s="11">
+        <v>47.6</v>
+      </c>
+      <c r="K171" s="11">
+        <v>57.1</v>
+      </c>
+      <c r="L171" s="11">
+        <v>59.5</v>
+      </c>
+      <c r="M171" s="11">
+        <v>45.2</v>
+      </c>
+      <c r="N171" s="15">
+        <v>25</v>
+      </c>
+      <c r="O171" s="15">
+        <v>30</v>
+      </c>
+      <c r="P171" s="15">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -51592,7 +51911,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -51605,7 +51923,7 @@
   <sheetPr codeName="工作表7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
@@ -51621,90 +51939,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="27" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="N2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -60056,8 +60374,59 @@
         <v>55</v>
       </c>
     </row>
+    <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B171" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="C171" s="16">
+        <v>64.3</v>
+      </c>
+      <c r="D171" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="E171" s="16">
+        <v>60.7</v>
+      </c>
+      <c r="F171" s="16">
+        <v>58.3</v>
+      </c>
+      <c r="G171" s="16">
+        <v>58.3</v>
+      </c>
+      <c r="H171" s="16">
+        <v>46.4</v>
+      </c>
+      <c r="I171" s="16">
+        <v>84.5</v>
+      </c>
+      <c r="J171" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="K171" s="16">
+        <v>60.7</v>
+      </c>
+      <c r="L171" s="16">
+        <v>60.7</v>
+      </c>
+      <c r="M171" s="16">
+        <v>63.1</v>
+      </c>
+      <c r="N171" s="18">
+        <v>40</v>
+      </c>
+      <c r="O171" s="18">
+        <v>36</v>
+      </c>
+      <c r="P171" s="18">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
@@ -60074,7 +60443,6 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
